--- a/examples/Templates/Excel/Consolidado.xlsx
+++ b/examples/Templates/Excel/Consolidado.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Proceso</t>
   </si>
@@ -31,38 +31,14 @@
     <t>Decisión</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>{{#each proceso.interviews}}{{proceso.file.name}}</t>
-  </si>
-  <si>
-    <t>{{proceso.role}}</t>
-  </si>
-  <si>
-    <t>{{proceso.priority}}</t>
-  </si>
-  <si>
-    <t>{{interviews.interviewed}}</t>
-  </si>
-  <si>
-    <t>{{interviews.tech rating | stars}}</t>
-  </si>
-  <si>
-    <t>{{interviews.decision}}</t>
-  </si>
-  <si>
-    <t>{{@index}}/{{@count}}</t>
-  </si>
-  <si>
-    <t>Total</t>
+    <t>Promedio tech</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -70,16 +46,33 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -87,12 +80,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,61 +435,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E3">
-        <f>SUM(E2:E2)</f>
+        <f>AVERAGE(E2:E2)</f>
       </c>
     </row>
   </sheetData>
